--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5552,8 +5682,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5576,1496 +5710,1617 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">태평가 — 민요채보-2/태평가.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">태평가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="G3" s="18"/>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">찾</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="18"/>
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O3" s="18"/>
+      <c r="P3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="Q3" s="18"/>
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="2"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U3" s="18"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="19"/>
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M4" s="19"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢
 無</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="19"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="G5" s="20"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="18"/>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">필</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">필</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="18"/>
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="18"/>
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="S6" s="18"/>
+      <c r="T6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="U6" s="18"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E7" s="19"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">재</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="19"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="19"/>
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="M7" s="19"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="19"/>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="20"/>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 浹</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="U8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="G9" s="18"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="18"/>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O9" s="18"/>
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q9" s="18"/>
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="G10" s="19"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="19"/>
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">철</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="Q10" s="19"/>
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 浹</t>
         </is>
       </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="20"/>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="20"/>
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 浹</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="U11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">미</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="O12" s="18"/>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="18"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="T13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">찾</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">찾</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">태평가 — 민요채보-2/태평가.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U14" s="20"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">태평가</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="T17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="U17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="17"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U18" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="S19" s="20"/>
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="U19" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S20" s="18"/>
+      <c r="T20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="U20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="17"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="S21" s="19"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U21" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U22" s="20"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="S23" s="18"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="18"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="17"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="S24" s="19"/>
+      <c r="T24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="U24" s="19"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S25" s="20"/>
+      <c r="T25" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="U25" s="20"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="17"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S27" s="19"/>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S28" s="20"/>
+      <c r="T28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U28" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -983,12 +983,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="3"/>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I79" s="2"/>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3897,12 +3897,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I100" s="2"/>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I108" s="2"/>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4941,7 +4941,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="10"/>
@@ -4987,7 +4987,7 @@
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="10"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="8"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="9"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="10"/>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O8" s="10"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="10"/>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="8"/>
@@ -5653,7 +5653,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
@@ -5692,7 +5692,7 @@
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5710,13 +5710,13 @@
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="9"/>
@@ -5725,7 +5725,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="10"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="13"/>
@@ -5779,13 +5779,13 @@
       <c r="O14" s="10"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="10"/>
       <c r="R14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4726,120 +4767,120 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">태평가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">짜</t>
         </is>
@@ -4847,91 +4888,91 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니리</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">증</t>
         </is>
@@ -4939,76 +4980,76 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -5016,84 +5057,84 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">찾</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -5101,93 +5142,93 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리리</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5195,84 +5236,84 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5280,99 +5321,99 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이리</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 湳</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -5380,100 +5421,100 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 湳</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
@@ -5481,84 +5522,84 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="26"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="26"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5566,84 +5607,84 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5651,145 +5692,145 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
+      <c r="S13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
 湳</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">오오</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="26"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
+      <c r="S14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -4742,30 +4742,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -4840,7 +4840,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -4923,7 +4924,8 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">니리</t>
+          <t xml:space="preserve">니
+리</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -5182,7 +5184,8 @@
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리리</t>
+          <t xml:space="preserve">리
+리</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -5340,7 +5343,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이리</t>
+          <t xml:space="preserve">이
+리</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5361,7 +5365,8 @@
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -5372,7 +5377,8 @@
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -5796,7 +5802,8 @@
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">오오</t>
+          <t xml:space="preserve">오
+오</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4797,7 +4820,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -4807,7 +4830,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
@@ -4817,7 +4840,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4827,7 +4850,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -4838,7 +4861,7 @@
 黃</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 나</t>
@@ -4849,7 +4872,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4860,7 +4883,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -4871,7 +4894,7 @@
 無</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -4881,7 +4904,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">짜</t>
         </is>
@@ -4894,7 +4917,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4905,13 +4928,13 @@
 潢</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
@@ -4922,7 +4945,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 리</t>
@@ -4933,7 +4956,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -4944,7 +4967,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4954,7 +4977,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -4964,7 +4987,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4974,7 +4997,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S4" s="25" t="inlineStr">
+      <c r="S4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">증</t>
         </is>
@@ -4987,13 +5010,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5004,13 +5027,13 @@
 無</t>
         </is>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5020,27 +5043,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -5051,7 +5074,7 @@
 無</t>
         </is>
       </c>
-      <c r="S5" s="26" t="inlineStr">
+      <c r="S5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -5064,7 +5087,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">찾</t>
         </is>
@@ -5074,13 +5097,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -5090,7 +5113,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -5100,13 +5123,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="29"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -5116,7 +5139,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5126,7 +5149,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -5136,7 +5159,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -5150,7 +5173,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5161,7 +5184,7 @@
 湳</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5171,7 +5194,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5182,7 +5205,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 리</t>
@@ -5193,13 +5216,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -5209,7 +5232,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
@@ -5220,7 +5243,7 @@
 南</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5231,7 +5254,7 @@
 南</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5245,7 +5268,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5256,7 +5279,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5266,13 +5289,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5282,13 +5305,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -5298,14 +5321,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="Q8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5316,7 +5339,7 @@
 潢</t>
         </is>
       </c>
-      <c r="S8" s="26" t="inlineStr">
+      <c r="S8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -5330,7 +5353,7 @@
 南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
@@ -5341,7 +5364,7 @@
 無</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 리</t>
@@ -5352,7 +5375,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -5363,7 +5386,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 나</t>
@@ -5375,7 +5398,7 @@
 湳</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 나</t>
@@ -5387,7 +5410,7 @@
 南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -5397,7 +5420,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -5408,7 +5431,7 @@
 南</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -5419,7 +5442,7 @@
 南</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -5433,7 +5456,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5443,7 +5466,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -5454,7 +5477,7 @@
 湳</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -5465,7 +5488,7 @@
 湳</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -5476,7 +5499,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -5487,7 +5510,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5498,7 +5521,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
@@ -5509,7 +5532,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
@@ -5520,7 +5543,7 @@
 姑</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
@@ -5533,7 +5556,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5544,7 +5567,7 @@
 無</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5555,7 +5578,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5565,20 +5588,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5589,13 +5612,13 @@
 無</t>
         </is>
       </c>
-      <c r="O11" s="26"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5605,7 +5628,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="26" t="inlineStr">
+      <c r="S11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5618,7 +5641,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5628,7 +5651,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
@@ -5638,7 +5661,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -5648,19 +5671,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -5670,7 +5693,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -5680,7 +5703,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5690,7 +5713,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5703,14 +5726,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -5720,7 +5743,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5730,27 +5753,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -5760,13 +5783,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5776,14 +5799,14 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
@@ -5793,14 +5816,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
 湳</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 오</t>
@@ -5811,33 +5834,33 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="32"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S14" s="26"/>
+      <c r="S14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,31 +227,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -369,7 +346,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 맨 오른쪽 율명 칸 1줄은 비어 있어 번호에서 제외, 내용 있는 오른쪽 첫 줄을 1로 9줄. 각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사(짜증을 내어서 무엇하나 / 성화를 내어서 무엇하나 / 인생 일장 춘몽인데 / 아니 노지는 못하리라 / 니나노 닐니리야 … / 얼싸 좋아 얼씨구 좋아 / 봄나비는 이리저리 펄펄 / 꽃을 찾아서 날아든다). 1~4·9줄의 姑는 氵 없이, 5~8줄(후렴)은 氵가 뚜렷해 㴌/㳞/湳으로 적음. 율명 옆 작은 점·쉼표형 꾸밈, 호선은 생략. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1076,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵 없이 黃으로 적힘(潢일 수도)</t>
+          <t xml:space="preserve">氵 없이 黃으로 보임</t>
         </is>
       </c>
       <c r="K14" s="2"/>
@@ -2487,7 +2464,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 글자 黃 흘림(潢 겹침?)</t>
+          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도)</t>
         </is>
       </c>
       <c r="K50" s="2"/>
@@ -2703,14 +2680,10 @@
 湳</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니나</t>
-        </is>
-      </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">위에 호선(○류) 꾸밈 생략</t>
+          <t xml:space="preserve">위에 호선 꾸밈 생략</t>
         </is>
       </c>
       <c r="K56" s="2"/>
@@ -2747,11 +2720,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노</t>
-        </is>
-      </c>
+      <c r="I57" s="2"/>
       <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
@@ -2895,7 +2864,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 ‿ 곡선 꾸밈 생략</t>
+          <t xml:space="preserve">아래 ‿ 곡선 생략</t>
         </is>
       </c>
       <c r="K61" s="2"/>
@@ -3460,19 +3429,23 @@
       <c r="F76" s="2">
         <v>1</v>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|黃</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="4"/>
+黃</t>
+        </is>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도)</t>
+        </is>
+      </c>
       <c r="K76" s="2"/>
     </row>
     <row r="77">
@@ -3858,7 +3831,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 '보'+'ㅁ'이 1~2정간에 걸쳐 쓰임</t>
+          <t xml:space="preserve">가사 보+ㅁ 세로로 씀</t>
         </is>
       </c>
       <c r="K86" s="2"/>
@@ -3884,19 +3857,27 @@
       <c r="F87" s="2">
         <v>1</v>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–|潢</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="I87" s="2"/>
-      <c r="J87" s="4"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 봄/몸? 1정간과 겹쳐 씀</t>
+        </is>
+      </c>
       <c r="K87" s="2"/>
     </row>
     <row r="88">
@@ -4232,27 +4213,23 @@
       <c r="F96" s="2">
         <v>4</v>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|南</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 '펄'의 흘림일 수도</t>
-        </is>
-      </c>
+      <c r="J96" s="4"/>
       <c r="K96" s="2"/>
     </row>
     <row r="97">
@@ -4788,7 +4765,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4813,14 +4790,14 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -4830,7 +4807,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
@@ -4840,7 +4817,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4850,7 +4827,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -4861,7 +4838,7 @@
 黃</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 나</t>
@@ -4872,7 +4849,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4883,7 +4860,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -4894,7 +4871,7 @@
 無</t>
         </is>
       </c>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -4904,37 +4881,41 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="29" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">짜</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
@@ -4945,7 +4926,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 리</t>
@@ -4956,7 +4937,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="31" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -4967,7 +4948,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4977,7 +4958,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="31" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -4987,7 +4968,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q4" s="31" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4997,870 +4978,861 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S4" s="31" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">증</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+黃</t>
+        </is>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">를</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="S5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">찾</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리
+리</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="32"/>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O8" s="27"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="Q8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="S8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">를</t>
-        </is>
-      </c>
-      <c r="R5" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+리</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니
+나</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="K9" s="24"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">못</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+姑</t>
+        </is>
+      </c>
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="S10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">찾</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">펄</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닐</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일</t>
-        </is>
-      </c>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
-        </is>
-      </c>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-湳</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리
-리</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장</t>
-        </is>
-      </c>
-      <c r="P7" s="21" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+仲</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="S7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="I8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
-        </is>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="Q8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="S8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">날</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-리</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니
-나</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-湳</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니
-나</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">못</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">춘</t>
-        </is>
-      </c>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="Q9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="S9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="S13" s="25"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">펄</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潕
 湳</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">씨</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-湳</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">노</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+오</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">몽</t>
-        </is>
-      </c>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엇</t>
-        </is>
-      </c>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="S10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엇</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">든</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="R11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">펄</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="K12" s="29"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인</t>
-        </is>
-      </c>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-南</t>
-        </is>
-      </c>
-      <c r="O13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">데</t>
-        </is>
-      </c>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">펄</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕
-湳</t>
-        </is>
-      </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오
-오</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M14" s="32"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="O14" s="32"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="S14" s="32"/>
+      <c r="S14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -2448,13 +2448,13 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|黃</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
+無</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도)</t>
+          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도); 아래 ㄴ머리 → 無(1-3 등 潢|無 가락과 같음)</t>
         </is>
       </c>
       <c r="K50" s="2"/>
@@ -3431,19 +3431,19 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|黃</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
+無</t>
         </is>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도)</t>
+          <t xml:space="preserve">아래 글자 黃(왼쪽 ㄱ획, 潢일 수도); 아래 ㄴ머리 → 無(1-3 등 潢|無 가락과 같음)</t>
         </is>
       </c>
       <c r="K76" s="2"/>
@@ -4835,7 +4835,7 @@
       <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
+無</t>
         </is>
       </c>
       <c r="K3" s="24" t="inlineStr">
@@ -5005,7 +5005,7 @@
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
+無</t>
         </is>
       </c>
       <c r="G5" s="28"/>

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -564,10 +564,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -510,17 +510,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -637,7 +637,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -695,6 +695,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4459,664 +4503,664 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:S14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="76.92" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="25"/>
+      <c r="H5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="7" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="24" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="19"/>
+      <c r="L6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="22"/>
+      <c r="L7" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="S7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="24"/>
+      <c r="L8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="7" t="s">
+      <c r="O8" s="24"/>
+      <c r="P8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="Q8" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="R8" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="21"/>
+      <c r="L9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="S9" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="22"/>
+      <c r="L10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="S10" s="22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="24"/>
+      <c r="J11" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="24"/>
+      <c r="L11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="7" t="s">
+      <c r="O11" s="24"/>
+      <c r="P11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="Q11" s="13" t="s">
+      <c r="Q11" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="R11" s="7" t="s">
+      <c r="R11" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="S11" s="13" t="s">
+      <c r="S11" s="24" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="19"/>
+      <c r="J12" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="19"/>
+      <c r="L12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="S12" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="22"/>
+      <c r="N13" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="7" t="s">
+      <c r="Q13" s="22"/>
+      <c r="R13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="S13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="S13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="25"/>
+      <c r="L14" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="24"/>
+      <c r="N14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="24"/>
+      <c r="P14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="7" t="s">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="S14" s="13"/>
+      <c r="S14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5124,7 +5168,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="67" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/태평가.xlsx
+++ b/sheets/민요/검수/태평가.xlsx
@@ -4509,28 +4509,28 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="76.92" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.43" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="R2" s="17"/>
       <c r="S2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>53</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>53</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>69</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>53</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>56</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>59</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>56</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>63</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>65</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>67</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>69</v>
       </c>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.62" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="106.4" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>71</v>
       </c>
@@ -5168,7 +5168,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
